--- a/output/CVE_20260815.xlsx
+++ b/output/CVE_20260815.xlsx
@@ -552,7 +552,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>&gt;=3.3.0,&lt;4.6.2</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -588,7 +588,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>[버전범위 불명확] jupyterlab is an extensible environment for interactive and reproducible computing, based on the Jupyter Notebook Architecture. From 3.3.0 until 4.5.10 and 4.6.2, JupyterLab allows notebook settings to be shared and applied through an overrides.json file using the Import button in the Settings Editor. In packages/notebook-extension/schema/tracker.json and packages/notebook-extension/src/index.ts, the sideBySideLeftMarginOverride and sideBySideRightMarginOverride settings are not properly validated before being inserted into style content, allowing a crafted settings file to contain instructions that execute as code instead of only changing display preferences. A user can import the malicious file, or an attacker with access to a shared settings location can plant an overrides.json that is applied automatically. The embedded code runs with the affected user's access and can read or modify notebooks and files and run code through the notebook server, including on a connected k</t>
+          <t>jupyterlab is an extensible environment for interactive and reproducible computing, based on the Jupyter Notebook Architecture. From 3.3.0 until 4.5.10 and 4.6.2, JupyterLab allows notebook settings to be shared and applied through an overrides.json file using the Import button in the Settings Editor. In packages/notebook-extension/schema/tracker.json and packages/notebook-extension/src/index.ts, the sideBySideLeftMarginOverride and sideBySideRightMarginOverride settings are not properly validated before being inserted into style content, allowing a crafted settings file to contain instructions that execute as code instead of only changing display preferences. A user can import the malicious file, or an attacker with access to a shared settings location can plant an overrides.json that is applied automatically. The embedded code runs with the affected user's access and can read or modify notebooks and files and run code through the notebook server, including on a connected k</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>20260815211219</t>
+          <t>20260816211125</t>
         </is>
       </c>
     </row>
@@ -630,7 +630,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>&lt;1.123.67|&lt;2.31.5|&lt;2.32.1</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -666,7 +666,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>[버전범위 불명확] n8n before 1.123.67, 2.x before 2.31.5, and 2.32.x before 2.32.1 contain a type confusion vulnerability in the Send Email node, which does not enforce that its message fields are strings. A crafted non-string value supplied from a workflow expression into the text or HTML body field can be interpreted by the underlying mail library (Nodemailer) as a file path or URL, allowing arbitrary local file disclosure and server-side request forgery (SSRF). Exploitation requires a pre-existing active workflow with an unauthenticated webhook, valid SMTP credentials configured on the node, and untrusted input mapped directly into the body field; this is not a default configuration.</t>
+          <t>n8n before 1.123.67, 2.x before 2.31.5, and 2.32.x before 2.32.1 contain a type confusion vulnerability in the Send Email node, which does not enforce that its message fields are strings. A crafted non-string value supplied from a workflow expression into the text or HTML body field can be interpreted by the underlying mail library (Nodemailer) as a file path or URL, allowing arbitrary local file disclosure and server-side request forgery (SSRF). Exploitation requires a pre-existing active workflow with an unauthenticated webhook, valid SMTP credentials configured on the node, and untrusted input mapped directly into the body field; this is not a default configuration.</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>20260815211219</t>
+          <t>20260816211125</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>&lt;2.32.1</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
@@ -744,7 +744,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>[버전범위 불명확] n8n versions before 2.32.1 fail to enforce the Allowed HTTP Request Domains allowlist in multiple AI and LLM nodes when user-supplied base or endpoint URLs are configured. Low-privileged workflow editors with use-only access to shared credentials can redirect requests to attacker-controlled hosts and exfiltrate credential secrets for reuse against underlying services.</t>
+          <t>n8n versions before 2.32.1 fail to enforce the Allowed HTTP Request Domains allowlist in multiple AI and LLM nodes when user-supplied base or endpoint URLs are configured. Low-privileged workflow editors with use-only access to shared credentials can redirect requests to attacker-controlled hosts and exfiltrate credential secrets for reuse against underlying services.</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20260815211219</t>
+          <t>20260816211125</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>&gt;=4.5.0,&lt;4.6.2</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -900,7 +900,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>[버전범위 불명확] jupyterlab is an extensible environment for interactive and reproducible computing, based on the Jupyter Notebook Architecture. From 4.5.0 until 4.5.10 and 4.6.2, in jupyterlab/extensions/manager.py and jupyterlab/extensions/pypi.py, JupyterLab's PyPI extension manager enforces blocked_extensions_uris by comparing requested install names to blocklist entries with custom normalization that is weaker than PyPI package-name canonicalization. An authenticated user can request a PyPI-equivalent spelling such as JupyterLab.Git for a blocklisted package such as jupyterlab-git, and JupyterLab accepts the install request even though pip resolves the variant to the same package. Security impact requires an allowlist or blocklist intended to restrict package installation, the PyPI Extension Manager, and kernels and terminals that are disabled or delegated to remote hosts. The bypass lets an authenticated user install a prohibited extension, defeat integrity restrictions, and affect ava</t>
+          <t>jupyterlab is an extensible environment for interactive and reproducible computing, based on the Jupyter Notebook Architecture. From 4.5.0 until 4.5.10 and 4.6.2, in jupyterlab/extensions/manager.py and jupyterlab/extensions/pypi.py, JupyterLab's PyPI extension manager enforces blocked_extensions_uris by comparing requested install names to blocklist entries with custom normalization that is weaker than PyPI package-name canonicalization. An authenticated user can request a PyPI-equivalent spelling such as JupyterLab.Git for a blocklisted package such as jupyterlab-git, and JupyterLab accepts the install request even though pip resolves the variant to the same package. Security impact requires an allowlist or blocklist intended to restrict package installation, the PyPI Extension Manager, and kernels and terminals that are disabled or delegated to remote hosts. The bypass lets an authenticated user install a prohibited extension, defeat integrity restrictions, and affect ava</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>&lt;2.32.1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -978,7 +978,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>[버전범위 불명확] n8n before 1.123.67, 2.31.5, and 2.32.1 contains a SQL injection vulnerability in the Snowflake node's Execute Query operation, which interpolates expression values directly into the SQL string. When a workflow author embeds untrusted, externally-controlled expression data directly in a raw SQL query, that data is not parameterized, allowing SQL injection. The fix adds an optional 'Query Parameters' field to bind values via positional placeholders.</t>
+          <t>n8n before 1.123.67, 2.31.5, and 2.32.1 contains a SQL injection vulnerability in the Snowflake node's Execute Query operation, which interpolates expression values directly into the SQL string. When a workflow author embeds untrusted, externally-controlled expression data directly in a raw SQL query, that data is not parameterized, allowing SQL injection. The fix adds an optional 'Query Parameters' field to bind values via positional placeholders.</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20260815211219</t>
+          <t>20260816211125</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>20260815211327</t>
+          <t>20260817205333</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>20260813</t>
+          <t>20260815</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>20260815</t>
+          <t>20260817</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/output/CVE_20260815.xlsx
+++ b/output/CVE_20260815.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>jupyterlab is an extensible environment for interactive and reproducible computing, based on the Jupyter Notebook Architecture. From 3.3.0 until 4.5.10 and 4.6.2, JupyterLab allows notebook settings to be shared and applied through an overrides.json file using the Import button in the Settings Editor. In packages/notebook-extension/schema/tracker.json and packages/notebook-extension/src/index.ts, the sideBySideLeftMarginOverride and sideBySideRightMarginOverride settings are not properly validated before being inserted into style content, allowing a crafted settings file to contain instructions that execute as code instead of only changing display preferences. A user can import the malicious file, or an attacker with access to a shared settings location can plant an overrides.json that is applied automatically. The embedded code runs with the affected user's access and can read or modify notebooks and files and run code through the notebook server, including on a connected k</t>
+          <t>jupyterlab은 Jupyter 노트북 아키텍처를 기반으로 하는 대화형 및 재현 가능한 컴퓨팅을 위한 확장 가능한 환경입니다. 3.3.0부터 4.5.10 및 4.6.2까지 JupyterLab에서는 설정 편집기의 가져오기 버튼을 사용하여 overrides.json 파일을 통해 노트북 설정을 공유하고 적용할 수 있습니다. packages/notebook-extension/schema/tracker.json 및 packages/notebook-extension/src/index.ts에서 sideBySideLeftMarginOverride 및 sideBySideRightMarginOverride 설정은 스타일 콘텐츠에 삽입되기 전에 제대로 검증되지 않으므로 조작된 설정 파일에 디스플레이 기본 설정만 변경하는 대신 코드로 실행되는 명령이 포함될 수 있습니다. 사용자가 악성 파일을 가져오거나, 공유 설정 위치에 액세스할 수 있는 공격자가 자동으로 적용되는 overrides.json을 심을 수 있습니다. 내장된 코드는 영향을 받는 사용자의 액세스 권한으로 실행되며 노트북과 파일을 읽거나 수정할 수 있고 연결된 k를 포함하여 노트북 서버를 통해 코드를 실행할 수 있습니다.</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>n8n before 1.123.67, 2.x before 2.31.5, and 2.32.x before 2.32.1 contain a type confusion vulnerability in the Send Email node, which does not enforce that its message fields are strings. A crafted non-string value supplied from a workflow expression into the text or HTML body field can be interpreted by the underlying mail library (Nodemailer) as a file path or URL, allowing arbitrary local file disclosure and server-side request forgery (SSRF). Exploitation requires a pre-existing active workflow with an unauthenticated webhook, valid SMTP credentials configured on the node, and untrusted input mapped directly into the body field; this is not a default configuration.</t>
+          <t>1.123.67 이전의 n8n, 2.31.5 이전의 2.x 및 2.32.1 이전의 2.32.x에는 메시지 필드가 문자열임을 강제하지 않는 Send Email 노드에 유형 혼동 취약점이 포함되어 있습니다. 워크플로 표현식에서 텍스트 또는 HTML 본문 필드로 제공되는 조작된 문자열이 아닌 값은 기본 메일 라이브러리(Nodemailer)에 의해 파일 경로 또는 URL로 해석될 수 있으므로 임의의 로컬 파일 공개 및 서버측 요청 위조(SSRF)가 허용됩니다. 악용하려면 인증되지 않은 웹훅, 노드에 구성된 유효한 SMTP 자격 증명, 본문 필드에 직접 매핑된 신뢰할 수 없는 입력이 포함된 기존 활성 워크플로가 필요합니다. 이는 기본 구성이 아닙니다.</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>n8n versions before 2.32.1 fail to enforce the Allowed HTTP Request Domains allowlist in multiple AI and LLM nodes when user-supplied base or endpoint URLs are configured. Low-privileged workflow editors with use-only access to shared credentials can redirect requests to attacker-controlled hosts and exfiltrate credential secrets for reuse against underlying services.</t>
+          <t>2.32.1 이전의 n8n 버전은 사용자가 제공한 기본 또는 엔드포인트 URL이 구성된 경우 여러 AI 및 LLM 노드에서 허용된 HTTP 요청 도메인 허용 목록을 적용하지 못합니다. 공유 자격 증명에 대한 사용 전용 액세스 권한이 있는 낮은 권한의 워크플로 편집자는 공격자가 제어하는 ​​호스트로 요청을 리디렉션하고 기본 서비스에 재사용하기 위해 자격 증명 비밀을 유출할 수 있습니다.</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>JupyterLab's image viewer allows for cross-site scripting (XSS) when a specially-crafted image file is opened through the image viewer and then opened in a new tab. This XSS issue can be used to cause remote code execution (RCE) on the JupyterLab server. ### Impact This vulnerability allows for arbitrary code execution. ### Patches JupyterLab [`v4.6.2`](https://github.com/jupyterlab/jupyterlab/releases/tag/v4.6.2) and [`v4.5.10`](https://github.com/jupyterlab/jupyterlab/releases/tag/v4.5.10) contain the patch. ### Workarounds Disable the image viewer plugin: ``` jupyter labextension disable @jupyterlab/imageviewer-extension:plugin ``` Confirm with: ``` jupyter labextension list ```</t>
+          <t>JupyterLab의 이미지 뷰어는 특별히 제작된 이미지 파일을 이미지 뷰어를 통해 연 다음 새 탭에서 열 때 XSS(교차 사이트 스크립팅)를 허용합니다. 이 XSS 문제는 JupyterLab 서버에서 원격 코드 실행(RCE)을 유발하는 데 사용될 수 있습니다. ### 영향 이 취약점으로 인해 임의 코드 실행이 허용됩니다. ### 패치 JupyterLab [`v4.6.2`](https://github.com/jupyterlab/jupyterlab/releases/tag/v4.6.2) 및 [`v4.5.10`](https://github.com/jupyterlab/jupyterlab/releases/tag/v4.5.10)에는 패치가 포함되어 있습니다. ### 해결 방법 이미지 뷰어 플러그인을 비활성화합니다. ``` jupyter labextension 비활성화 @jupyterlab/imageviewer-extension:plugin ``` 확인: ``` jupyter labextension list ```</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>jupyterlab is an extensible environment for interactive and reproducible computing, based on the Jupyter Notebook Architecture. From 4.5.0 until 4.5.10 and 4.6.2, in jupyterlab/extensions/manager.py and jupyterlab/extensions/pypi.py, JupyterLab's PyPI extension manager enforces blocked_extensions_uris by comparing requested install names to blocklist entries with custom normalization that is weaker than PyPI package-name canonicalization. An authenticated user can request a PyPI-equivalent spelling such as JupyterLab.Git for a blocklisted package such as jupyterlab-git, and JupyterLab accepts the install request even though pip resolves the variant to the same package. Security impact requires an allowlist or blocklist intended to restrict package installation, the PyPI Extension Manager, and kernels and terminals that are disabled or delegated to remote hosts. The bypass lets an authenticated user install a prohibited extension, defeat integrity restrictions, and affect ava</t>
+          <t>jupyterlab은 Jupyter 노트북 아키텍처를 기반으로 하는 대화형 및 재현 가능한 컴퓨팅을 위한 확장 가능한 환경입니다. 4.5.0부터 4.5.10 및 4.6.2까지 jupyterlab/extensions/manager.py 및 jupyterlab/extensions/pypi.py에서 JupyterLab의 PyPI 확장 관리자는 요청된 설치 이름을 PyPI 패키지 이름 정규화보다 약한 사용자 정의 정규화를 사용하는 차단 목록 항목과 비교하여 Blocked_extensions_uris를 적용합니다. 인증된 사용자는 jupyterlab-git과 같은 차단 목록 패키지에 대해 JupyterLab.Git와 같은 PyPI와 동등한 철자를 요청할 수 있으며, pip가 변형을 동일한 패키지로 확인하더라도 JupyterLab은 설치 요청을 수락합니다. 보안에 영향을 미치려면 패키지 설치, PyPI 확장 관리자, 비활성화되거나 원격 호스트에 위임된 커널 및 터미널을 제한하기 위한 허용 목록 또는 차단 목록이 필요합니다. 우회를 통해 인증된 사용자는 금지된 확장 프로그램을 설치하고 무결성 제한을 해제하며 ava에 영향을 미칠 수 있습니다.</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>n8n before 1.123.67, 2.31.5, and 2.32.1 contains a SQL injection vulnerability in the Snowflake node's Execute Query operation, which interpolates expression values directly into the SQL string. When a workflow author embeds untrusted, externally-controlled expression data directly in a raw SQL query, that data is not parameterized, allowing SQL injection. The fix adds an optional 'Query Parameters' field to bind values via positional placeholders.</t>
+          <t>1.123.67, 2.31.5 및 2.32.1 이전의 n8n에는 표현식 값을 SQL 문자열에 직접 보간하는 Snowflake 노드의 쿼리 실행 작업에 SQL 주입 취약점이 포함되어 있습니다. 워크플로 작성자가 신뢰할 수 없고 외부에서 제어되는 식 데이터를 원시 SQL 쿼리에 직접 포함하는 경우 해당 데이터는 매개 변수화되지 않으므로 SQL 삽입이 허용됩니다. 이 수정 사항은 위치 자리 표시자를 통해 값을 바인딩하기 위한 선택적 '쿼리 매개 변수' 필드를 추가합니다.</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>20260817205333</t>
+          <t>20260817214713</t>
         </is>
       </c>
     </row>
